--- a/LATEST_SCHEMA/schema_dbo_mssql_dbo_mssql.xlsx
+++ b/LATEST_SCHEMA/schema_dbo_mssql_dbo_mssql.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceSystem" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataQualityFindings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="customers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="employees" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="purchase_order_items" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="purchase_orders" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales_order_items" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales_orders" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stores" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="suppliers" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__rt_meta" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__rt_payload" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SourceSystem" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="DataQualityFindings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="customers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="employees" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="inventory" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="products" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="purchase_order_items" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="purchase_orders" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="sales_order_items" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="sales_orders" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="stores" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="suppliers" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="__rt_meta" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet name="__rt_payload" sheetId="16" state="hidden" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DataQualityFindings'!$A$1:$Z$65</definedName>
@@ -832,7 +832,7 @@
     <col width="25" customWidth="1" min="12" max="12"/>
     <col width="25" customWidth="1" min="13" max="13"/>
     <col width="80" customWidth="1" min="14" max="14"/>
-    <col width="52" customWidth="1" min="15" max="15"/>
+    <col width="67" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1474,7 +1474,11 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Primary key for the purchase order record.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -1548,7 +1552,11 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Foreign key referencing suppliers.supplier_id for the purchase order record.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -1622,7 +1630,11 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Foreign key referencing stores.store_id for the purchase order record.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -1704,14 +1716,18 @@
           <t>category</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Category value for the purchase order record.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>entity.status</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -1720,12 +1736,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"]</t>
+          <t>["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched","cross-table consensus: 2 similar columns"]</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>["name","profile","type","values"]</t>
+          <t>["cross_table_consensus","name","profile","type"]</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -1786,14 +1802,18 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Timestamp value for the purchase order record.</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -1802,12 +1822,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"]</t>
+          <t>["name token: order_date","type hint: date","legacy field classification: temporal","table context: purchase_orders","cross-table consensus: 2 similar columns"]</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>["name","profile","table_context","type","values"]</t>
+          <t>["cross_table_consensus","name","profile","table_context","type"]</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -1868,14 +1888,18 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Timestamp value for the purchase order record.</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -1884,12 +1908,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"]</t>
+          <t>["name token: expected_date","type hint: date","legacy field classification: temporal","table context: purchase_orders"]</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>["name","profile","table_context","type","values"]</t>
+          <t>["name","profile","table_context","type"]</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -1950,14 +1974,18 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Timestamp when the purchase order record was created.</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -1966,12 +1994,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"]</t>
+          <t>["name token: created_at","type hint: datetime2","legacy field classification: temporal","table context: purchase_orders","cross-table consensus: 10 similar columns"]</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>["name","profile","table_context","type","values"]</t>
+          <t>["cross_table_consensus","name","profile","table_context","type"]</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -2032,14 +2060,18 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Timestamp when the purchase order record was last updated.</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2048,12 +2080,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"]</t>
+          <t>["name token: updated_at","type hint: datetime2","legacy field classification: temporal","table context: purchase_orders","cross-table consensus: 10 similar columns"]</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>["name","profile","table_context","type","values"]</t>
+          <t>["cross_table_consensus","name","profile","table_context","type"]</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -2106,7 +2138,11 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Approver employee foreign key for procurement workflow.</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -3162,7 +3198,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3276,7 +3312,11 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Primary key for the sales order item record.</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -3350,7 +3390,11 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Foreign key referencing sales_orders.sales_order_id for the sales order item record.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -3428,7 +3472,11 @@
           <t>product_identifier</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Foreign key referencing products.product_id for the sales order item record.</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -3510,7 +3558,11 @@
           <t>quantity</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Quantity value for the sales order item record.</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -3608,7 +3660,11 @@
           <t>currency_amount</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Currency amount value for the sales order item record.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -3690,7 +3746,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Timestamp when the sales order item record was created.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -3772,7 +3832,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Timestamp when the sales order item record was last updated.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -3854,7 +3918,11 @@
           <t>quantity</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Quantity value for the sales order item record.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -3944,7 +4012,11 @@
           <t>quantity</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sold quantity unit (ea/box).</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -5080,7 +5152,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -5194,7 +5266,11 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Primary key for the sales order record.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -5268,7 +5344,11 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Foreign key referencing stores.store_id for the sales order record.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -5350,7 +5430,11 @@
           <t>customer_identifier</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Foreign key referencing customers.customer_id for the sales order record.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -5424,7 +5508,11 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Foreign key referencing employees.employee_id for the sales order record.</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -5506,7 +5594,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Timestamp value for the sales order record.</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
@@ -5588,7 +5680,11 @@
           <t>category</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Category value for the sales order record.</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
           <t>entity.status</t>
@@ -5670,7 +5766,11 @@
           <t>currency_amount</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Currency amount value for the sales order record.</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -5752,7 +5852,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Timestamp when the sales order record was created.</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -5834,7 +5938,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Timestamp when the sales order record was last updated.</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -5908,7 +6016,11 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sales representative foreign key for order ownership.</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -6612,7 +6724,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Stores store records including name, code, and address.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]}</t>
@@ -6822,7 +6938,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -6936,7 +7052,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Primary key for the store record.</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -7010,7 +7130,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Name stored for the store record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -7084,7 +7208,11 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Code stored for the store record as nvarchar(450).</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
         <v>0.1</v>
@@ -7154,7 +7282,11 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Address stored for the store record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>contact.address</t>
@@ -7228,7 +7360,11 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>City stored for the store record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
         <v>0.1</v>
@@ -7294,7 +7430,11 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>State stored for the store record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="n">
         <v>0.1</v>
@@ -7364,7 +7504,11 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Postal code stored for the store record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>contact.address</t>
@@ -7450,7 +7594,11 @@
           <t>contact</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Contact value for the store record.</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>contact.phone</t>
@@ -7532,7 +7680,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Timestamp when the store record was created.</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -7614,7 +7766,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Timestamp when the store record was last updated.</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -8620,7 +8776,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Stores supplier records including name, contact name, and email.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]}</t>
@@ -8830,7 +8990,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -8944,7 +9104,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Primary key for the supplier record.</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -9018,7 +9182,11 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Name stored for the supplier record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -9100,7 +9268,11 @@
           <t>person_name</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Person name value for the supplier record.</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -9178,7 +9350,11 @@
           <t>contact</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Contact value for the supplier record.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>contact.email</t>
@@ -9264,7 +9440,11 @@
           <t>contact</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Contact value for the supplier record.</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>contact.phone</t>
@@ -9346,7 +9526,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Timestamp when the supplier record was created.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -9428,7 +9612,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Timestamp when the supplier record was last updated.</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -10007,7 +10195,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"metadata":{"generated_at":"2026-03-27T09:48:10.142923+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail</t>
+          <t>{"metadata":{"generated_at":"2026-03-27T10:53:39.953991+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":0.97,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["cross_table_consensus","name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":0.99,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.89,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":0.99,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the customer record.","cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Given name value for the customer record.","cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Family name value for the customer record.","cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Contact value for the customer record.","cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Contact value for the customer record.","cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the customer record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the customer record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"Stores customer records including first name, last name, and email.","primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the employee record.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing stores.store_id for the employee record.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Given name value for the employee record.","cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Family name value for the employee record.","cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Contact value for the employee record.","cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Role stored for the employee record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"Timestamp value for the employee record.","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the employee record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the employee record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"Stores employee records including first name, last name, and email.","primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the inventory record.","cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing stores.store_id for the inventory record.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing products.product_id for the inventory record.","cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Quantity value for the inventory record.","cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Reorder level stored for the inventory record as integer.","cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"Timestamp value for the inventory record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the inventory record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the inventory record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Stock value stored for the inventory record as numeric(10,2).","cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_c</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10205,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column sh</t>
+          <t>olumns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the product record.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing suppliers.supplier_id for the product record.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Product identifier value for the product record.","cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Name stored for the product record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Category value for the product record.","cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Currency amount value for the product record.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Currency amount value for the product record.","cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Status flag indicating whether the product record is active or deleted.","cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the product record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the product record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Mass value for the product record.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Length value for the product record.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Product description stored for the product record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the purchase order item record.","cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing purchase_orders.po_id for the purchase order item record.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing products.product_id for the purchase order item record.","cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"Quantity value for the purchase order item record.","cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Currency amount value for the purchase order item record.","cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the purchase order item record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the purchase order item record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Quantity value for the purchase order item record.","cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the purchase order record.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing suppliers.supplier_id for the purchase order record.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing stores.store_id for the purchase order record.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Category value for the purchase order record.","cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":0.95,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","type"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"Timestamp value for the purchase order record.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","table context: purchase_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"Timestamp value for the purchase order record.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10215,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ould always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendati</t>
+          <t>","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.75,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the purchase order record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":0.9,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","table context: purchase_orders","cross-table consensus: 10 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the purchase order record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":0.9,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","table context: purchase_orders","cross-table consensus: 10 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the sales order item record.","cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing sales_orders.sales_order_id for the sales order item record.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing products.product_id for the sales order item record.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"Quantity value for the sales order item record.","cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"Currency amount value for the sales order item record.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the sales order item record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the sales order item record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Quantity value for the sales order item record.","cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the sales order record.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing stores.store_id for the sales order record.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Foreign key referencing customers.customer_id for the sales order record.","cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Foreign key referencing employees.employee_id for the sales order record.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp value for the sales order record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Category value for the sales order record.","cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"Currency amount value for the sales order record.","cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the sales order record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the sales order record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the store record.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Name stored for the store record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Code stored for the store record as nvarchar(450).","cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Address stored for the store record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"City stored for the store record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":3,"null_count":0,"data_range":{"min":"Cork","max</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10225,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>on":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":null,"primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
+          <t>":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"State stored for the store record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Postal code stored for the store record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Contact value for the store record.","cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the store record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the store record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"Stores store records including name, code, and address.","primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Primary key for the supplier record.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Name stored for the supplier record as nvarchar collate \"sql_latin1_general_cp1_ci_as\".","cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Person name value for the supplier record.","cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Contact value for the supplier record.","cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Contact value for the supplier record.","cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Timestamp when the supplier record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Timestamp when the supplier record was last updated.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"Stores supplier records including name, contact name, and email.","primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10285,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>2026-03-27T09:48:10.142923+00:00</t>
+          <t>2026-03-27T10:53:39.953991+00:00</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -15332,7 +15520,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Stores customer records including first name, last name, and email.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]}</t>
@@ -15542,7 +15734,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -15664,7 +15856,11 @@
           <t>customer_identifier</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Primary key for the customer record.</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -15746,7 +15942,11 @@
           <t>given_name</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Given name value for the customer record.</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -15828,7 +16028,11 @@
           <t>family_name</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Family name value for the customer record.</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -15914,7 +16118,11 @@
           <t>contact</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Contact value for the customer record.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>contact.email</t>
@@ -16000,7 +16208,11 @@
           <t>contact</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Contact value for the customer record.</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>contact.phone</t>
@@ -16082,7 +16294,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Timestamp when the customer record was created.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -16164,7 +16380,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Timestamp when the customer record was last updated.</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -16804,7 +17024,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Stores employee records including first name, last name, and email.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]}</t>
@@ -17128,7 +17352,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -17242,7 +17466,11 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Primary key for the employee record.</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -17316,7 +17544,11 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Foreign key referencing stores.store_id for the employee record.</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -17398,7 +17630,11 @@
           <t>given_name</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Given name value for the employee record.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -17480,7 +17716,11 @@
           <t>family_name</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Family name value for the employee record.</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -17566,7 +17806,11 @@
           <t>contact</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Contact value for the employee record.</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>contact.email</t>
@@ -17640,7 +17884,11 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Role stored for the employee record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>entity.type</t>
@@ -17722,7 +17970,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Timestamp value for the employee record.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>temporal.date_only</t>
@@ -17804,7 +18056,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Timestamp when the employee record was created.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -17886,7 +18142,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Timestamp when the employee record was last updated.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -18902,7 +19162,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -19016,7 +19276,11 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Primary key for the inventory record.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -19090,7 +19354,11 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Foreign key referencing stores.store_id for the inventory record.</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -19168,7 +19436,11 @@
           <t>product_identifier</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Foreign key referencing products.product_id for the inventory record.</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -19250,7 +19522,11 @@
           <t>quantity</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Quantity value for the inventory record.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -19340,7 +19616,11 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Reorder level stored for the inventory record as integer.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>0.1</v>
@@ -19414,7 +19694,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Timestamp value for the inventory record.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>temporal.event_time</t>
@@ -19496,7 +19780,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Timestamp when the inventory record was created.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -19578,7 +19866,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Timestamp when the inventory record was last updated.</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -19652,7 +19944,11 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Stock value stored for the inventory record as numeric(10,2).</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>0</v>
@@ -19710,7 +20006,11 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Current stock unit label.</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>0.15</v>
@@ -20686,7 +20986,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -20804,7 +21104,11 @@
           <t>product_identifier</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Primary key for the product record.</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -20878,7 +21182,11 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Foreign key referencing suppliers.supplier_id for the product record.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -20956,7 +21264,11 @@
           <t>product_identifier</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Product identifier value for the product record.</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>identifier.product_code</t>
@@ -21030,7 +21342,11 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Name stored for the product record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>contact.person_name</t>
@@ -21112,7 +21428,11 @@
           <t>category</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Category value for the product record.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>entity.category</t>
@@ -21194,7 +21514,11 @@
           <t>currency_amount</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Currency amount value for the product record.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -21276,7 +21600,11 @@
           <t>currency_amount</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Currency amount value for the product record.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -21350,7 +21678,11 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Status flag indicating whether the product record is active or deleted.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>0</v>
@@ -21416,7 +21748,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Timestamp when the product record was created.</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -21498,7 +21834,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Timestamp when the product record was last updated.</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -21576,7 +21916,11 @@
           <t>mass</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Source weight unit (kg/lb) used for unit inference testing.</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
         <v>0.15</v>
@@ -21654,7 +21998,11 @@
           <t>mass</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Mass value for the product record.</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>0</v>
@@ -21732,7 +22080,11 @@
           <t>length</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Length value for the product record.</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>0</v>
@@ -21810,7 +22162,11 @@
           <t>length</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Source length unit (cm/in) used for unit inference testing.</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="n">
         <v>0.15</v>
@@ -21884,7 +22240,11 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Product description stored for the product record as nvarchar collate "sql_latin1_general_cp1_ci_as".</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>0.1</v>
@@ -21942,7 +22302,11 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Primary supplier relationship used for join candidate detection.</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -23184,7 +23548,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>column_description</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -23298,7 +23662,11 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Primary key for the purchase order item record.</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -23372,7 +23740,11 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Foreign key referencing purchase_orders.po_id for the purchase order item record.</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -23450,7 +23822,11 @@
           <t>product_identifier</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Foreign key referencing products.product_id for the purchase order item record.</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>identifier.foreign_key</t>
@@ -23532,7 +23908,11 @@
           <t>quantity</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Quantity value for the purchase order item record.</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -23630,7 +24010,11 @@
           <t>currency_amount</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Currency amount value for the purchase order item record.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>finance.currency_amount</t>
@@ -23712,7 +24096,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Timestamp when the purchase order item record was created.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>temporal.created_at</t>
@@ -23794,7 +24182,11 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Timestamp when the purchase order item record was last updated.</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>temporal.updated_at</t>
@@ -23876,7 +24268,11 @@
           <t>quantity</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Quantity value for the purchase order item record.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>measure.quantity</t>
@@ -23966,7 +24362,11 @@
           <t>quantity</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Ordered quantity unit (ea/box).</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>measure.quantity</t>
